--- a/Data/EXCEL/Transfer/salemon/202206/6634-salemon-202206.xlsx
+++ b/Data/EXCEL/Transfer/salemon/202206/6634-salemon-202206.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x15 xr xr6 xr10">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25225"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25330"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\linea\OneDrive\myStocksPGMs\V2.0\xls2xlsx\transfer\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORKSPACES\myStocksPGMs\V2.0\xls2xlsx\transfer\202206\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{747E17BA-9B47-404F-8477-4480649C2D4F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{90494DD1-4F32-493B-80B0-3173B804142D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3285" yWindow="2625" windowWidth="24465" windowHeight="12855"/>
+    <workbookView xWindow="945" yWindow="3600" windowWidth="26925" windowHeight="11205"/>
   </bookViews>
   <sheets>
     <sheet name="6634-salemon-202206" sheetId="2" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="366" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="368" uniqueCount="18">
   <si>
     <t>月別</t>
   </si>
@@ -261,7 +261,7 @@
     </font>
     <font>
       <sz val="10"/>
-      <color rgb="FF008000"/>
+      <color rgb="FFFF0000"/>
       <name val="新細明體"/>
       <family val="2"/>
       <charset val="136"/>
@@ -277,7 +277,7 @@
     </font>
     <font>
       <sz val="10"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FF008000"/>
       <name val="新細明體"/>
       <family val="2"/>
       <charset val="136"/>
@@ -1218,20 +1218,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Q66"/>
+  <dimension ref="A1:Q67"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="12.625" customWidth="1"/>
-    <col min="2" max="5" width="10.625" customWidth="1"/>
-    <col min="6" max="6" width="11.625" customWidth="1"/>
-    <col min="7" max="8" width="12.125" customWidth="1"/>
-    <col min="9" max="9" width="10.625" customWidth="1"/>
-    <col min="10" max="10" width="10.125" customWidth="1"/>
-    <col min="11" max="13" width="12.125" customWidth="1"/>
-    <col min="14" max="14" width="10.625" customWidth="1"/>
-    <col min="15" max="15" width="10.125" customWidth="1"/>
-    <col min="16" max="16" width="12.125" customWidth="1"/>
-    <col min="17" max="17" width="13.5" customWidth="1"/>
+    <col min="1" max="1" width="13.875" customWidth="1"/>
+    <col min="2" max="5" width="11.625" customWidth="1"/>
+    <col min="6" max="6" width="12.75" customWidth="1"/>
+    <col min="7" max="8" width="13.25" customWidth="1"/>
+    <col min="9" max="9" width="11.625" customWidth="1"/>
+    <col min="10" max="10" width="11.125" customWidth="1"/>
+    <col min="11" max="13" width="13.25" customWidth="1"/>
+    <col min="14" max="14" width="11.625" customWidth="1"/>
+    <col min="15" max="15" width="11.125" customWidth="1"/>
+    <col min="16" max="16" width="13.25" customWidth="1"/>
+    <col min="17" max="17" width="14.375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:17" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
@@ -1384,25 +1384,25 @@
     </row>
     <row r="5" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A5" s="6">
-        <v>44682</v>
+        <v>44713</v>
       </c>
       <c r="B5" s="7">
-        <v>82.3</v>
+        <v>80</v>
       </c>
       <c r="C5" s="7">
-        <v>80</v>
+        <v>85.2</v>
       </c>
       <c r="D5" s="7">
-        <v>83.3</v>
+        <v>90.9</v>
       </c>
       <c r="E5" s="7">
-        <v>77.099999999999994</v>
+        <v>78.2</v>
       </c>
       <c r="F5" s="8">
-        <v>-2.2999999999999998</v>
+        <v>5.2</v>
       </c>
       <c r="G5" s="8">
-        <v>-2.79</v>
+        <v>6.5</v>
       </c>
       <c r="H5" s="9">
         <v>0</v>
@@ -1410,14 +1410,14 @@
       <c r="I5" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="J5" s="8">
+      <c r="J5" s="10">
         <v>-100</v>
       </c>
       <c r="K5" s="9">
         <v>3.3E-3</v>
       </c>
-      <c r="L5" s="8">
-        <v>-93</v>
+      <c r="L5" s="10">
+        <v>-93.5</v>
       </c>
       <c r="M5" s="9">
         <v>0</v>
@@ -1425,37 +1425,37 @@
       <c r="N5" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="O5" s="8">
+      <c r="O5" s="10">
         <v>-100</v>
       </c>
       <c r="P5" s="9">
         <v>3.3E-3</v>
       </c>
-      <c r="Q5" s="8">
-        <v>-93</v>
+      <c r="Q5" s="10">
+        <v>-93.5</v>
       </c>
     </row>
     <row r="6" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A6" s="6">
-        <v>44652</v>
+        <v>44682</v>
       </c>
       <c r="B6" s="7">
-        <v>88.5</v>
+        <v>82.3</v>
       </c>
       <c r="C6" s="7">
-        <v>82.3</v>
+        <v>80</v>
       </c>
       <c r="D6" s="7">
-        <v>89.9</v>
+        <v>83.3</v>
       </c>
       <c r="E6" s="7">
-        <v>79.099999999999994</v>
-      </c>
-      <c r="F6" s="8">
-        <v>-6.2</v>
-      </c>
-      <c r="G6" s="8">
-        <v>-7.01</v>
+        <v>77.099999999999994</v>
+      </c>
+      <c r="F6" s="10">
+        <v>-2.2999999999999998</v>
+      </c>
+      <c r="G6" s="10">
+        <v>-2.79</v>
       </c>
       <c r="H6" s="9">
         <v>0</v>
@@ -1463,14 +1463,14 @@
       <c r="I6" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="J6" s="8">
+      <c r="J6" s="10">
         <v>-100</v>
       </c>
       <c r="K6" s="9">
         <v>3.3E-3</v>
       </c>
-      <c r="L6" s="8">
-        <v>-92.8</v>
+      <c r="L6" s="10">
+        <v>-93</v>
       </c>
       <c r="M6" s="9">
         <v>0</v>
@@ -1478,329 +1478,329 @@
       <c r="N6" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="O6" s="8">
+      <c r="O6" s="10">
         <v>-100</v>
       </c>
       <c r="P6" s="9">
         <v>3.3E-3</v>
       </c>
-      <c r="Q6" s="8">
-        <v>-92.8</v>
+      <c r="Q6" s="10">
+        <v>-93</v>
       </c>
     </row>
     <row r="7" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A7" s="6">
-        <v>44621</v>
+        <v>44652</v>
       </c>
       <c r="B7" s="7">
-        <v>86.3</v>
+        <v>88.5</v>
       </c>
       <c r="C7" s="7">
-        <v>88.5</v>
+        <v>82.3</v>
       </c>
       <c r="D7" s="7">
-        <v>92.9</v>
+        <v>89.9</v>
       </c>
       <c r="E7" s="7">
-        <v>80</v>
+        <v>79.099999999999994</v>
       </c>
       <c r="F7" s="10">
-        <v>2.2000000000000002</v>
+        <v>-6.2</v>
       </c>
       <c r="G7" s="10">
-        <v>2.5499999999999998</v>
+        <v>-7.01</v>
       </c>
       <c r="H7" s="9">
         <v>0</v>
       </c>
-      <c r="I7" s="8">
-        <v>-100</v>
-      </c>
-      <c r="J7" s="8">
+      <c r="I7" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J7" s="10">
         <v>-100</v>
       </c>
       <c r="K7" s="9">
         <v>3.3E-3</v>
       </c>
-      <c r="L7" s="8">
-        <v>-92</v>
+      <c r="L7" s="10">
+        <v>-92.8</v>
       </c>
       <c r="M7" s="9">
         <v>0</v>
       </c>
-      <c r="N7" s="8">
-        <v>-100</v>
-      </c>
-      <c r="O7" s="8">
+      <c r="N7" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="O7" s="10">
         <v>-100</v>
       </c>
       <c r="P7" s="9">
         <v>3.3E-3</v>
       </c>
-      <c r="Q7" s="8">
-        <v>-92</v>
+      <c r="Q7" s="10">
+        <v>-92.8</v>
       </c>
     </row>
     <row r="8" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A8" s="6">
-        <v>44593</v>
+        <v>44621</v>
       </c>
       <c r="B8" s="7">
-        <v>85</v>
+        <v>86.3</v>
       </c>
       <c r="C8" s="7">
-        <v>86.3</v>
+        <v>88.5</v>
       </c>
       <c r="D8" s="7">
-        <v>92.3</v>
+        <v>92.9</v>
       </c>
       <c r="E8" s="7">
-        <v>78</v>
-      </c>
-      <c r="F8" s="10">
-        <v>1.3</v>
-      </c>
-      <c r="G8" s="10">
-        <v>1.53</v>
+        <v>80</v>
+      </c>
+      <c r="F8" s="8">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="G8" s="8">
+        <v>2.5499999999999998</v>
       </c>
       <c r="H8" s="9">
-        <v>1E-3</v>
-      </c>
-      <c r="I8" s="8">
-        <v>-56.8</v>
-      </c>
-      <c r="J8" s="8">
-        <v>-80.099999999999994</v>
+        <v>0</v>
+      </c>
+      <c r="I8" s="10">
+        <v>-100</v>
+      </c>
+      <c r="J8" s="10">
+        <v>-100</v>
       </c>
       <c r="K8" s="9">
         <v>3.3E-3</v>
       </c>
-      <c r="L8" s="8">
-        <v>-89.6</v>
+      <c r="L8" s="10">
+        <v>-92</v>
       </c>
       <c r="M8" s="9">
-        <v>1E-3</v>
-      </c>
-      <c r="N8" s="8">
-        <v>-56.8</v>
-      </c>
-      <c r="O8" s="8">
-        <v>-80.099999999999994</v>
+        <v>0</v>
+      </c>
+      <c r="N8" s="10">
+        <v>-100</v>
+      </c>
+      <c r="O8" s="10">
+        <v>-100</v>
       </c>
       <c r="P8" s="9">
         <v>3.3E-3</v>
       </c>
-      <c r="Q8" s="8">
-        <v>-89.6</v>
+      <c r="Q8" s="10">
+        <v>-92</v>
       </c>
     </row>
     <row r="9" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A9" s="6">
-        <v>44562</v>
+        <v>44593</v>
       </c>
       <c r="B9" s="7">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="C9" s="7">
-        <v>85</v>
+        <v>86.3</v>
       </c>
       <c r="D9" s="7">
-        <v>87.7</v>
+        <v>92.3</v>
       </c>
       <c r="E9" s="7">
         <v>78</v>
       </c>
-      <c r="F9" s="10">
-        <v>3</v>
-      </c>
-      <c r="G9" s="10">
-        <v>3.66</v>
+      <c r="F9" s="8">
+        <v>1.3</v>
+      </c>
+      <c r="G9" s="8">
+        <v>1.53</v>
       </c>
       <c r="H9" s="9">
-        <v>2.3E-3</v>
+        <v>1E-3</v>
       </c>
       <c r="I9" s="10">
-        <v>14.5</v>
-      </c>
-      <c r="J9" s="8">
-        <v>-91.4</v>
+        <v>-56.8</v>
+      </c>
+      <c r="J9" s="10">
+        <v>-80.099999999999994</v>
       </c>
       <c r="K9" s="9">
-        <v>2.3E-3</v>
-      </c>
-      <c r="L9" s="8">
-        <v>-91.4</v>
+        <v>3.3E-3</v>
+      </c>
+      <c r="L9" s="10">
+        <v>-89.6</v>
       </c>
       <c r="M9" s="9">
-        <v>2.3E-3</v>
+        <v>1E-3</v>
       </c>
       <c r="N9" s="10">
-        <v>14.5</v>
-      </c>
-      <c r="O9" s="8">
-        <v>-91.4</v>
+        <v>-56.8</v>
+      </c>
+      <c r="O9" s="10">
+        <v>-80.099999999999994</v>
       </c>
       <c r="P9" s="9">
-        <v>2.3E-3</v>
-      </c>
-      <c r="Q9" s="8">
-        <v>-91.4</v>
+        <v>3.3E-3</v>
+      </c>
+      <c r="Q9" s="10">
+        <v>-89.6</v>
       </c>
     </row>
     <row r="10" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A10" s="6">
-        <v>44531</v>
+        <v>44562</v>
       </c>
       <c r="B10" s="7">
-        <v>78.099999999999994</v>
+        <v>82</v>
       </c>
       <c r="C10" s="7">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="D10" s="7">
-        <v>88.3</v>
+        <v>87.7</v>
       </c>
       <c r="E10" s="7">
-        <v>77</v>
-      </c>
-      <c r="F10" s="10">
-        <v>3.9</v>
-      </c>
-      <c r="G10" s="10">
-        <v>4.99</v>
+        <v>78</v>
+      </c>
+      <c r="F10" s="8">
+        <v>3</v>
+      </c>
+      <c r="G10" s="8">
+        <v>3.66</v>
       </c>
       <c r="H10" s="9">
-        <v>2E-3</v>
+        <v>2.3E-3</v>
       </c>
       <c r="I10" s="8">
-        <v>-29.8</v>
-      </c>
-      <c r="J10" s="8">
-        <v>-56.7</v>
+        <v>14.5</v>
+      </c>
+      <c r="J10" s="10">
+        <v>-91.4</v>
       </c>
       <c r="K10" s="9">
-        <v>6.2300000000000001E-2</v>
+        <v>2.3E-3</v>
       </c>
       <c r="L10" s="10">
-        <v>1248.3</v>
+        <v>-91.4</v>
       </c>
       <c r="M10" s="9">
-        <v>2E-3</v>
+        <v>2.3E-3</v>
       </c>
       <c r="N10" s="8">
-        <v>-29.8</v>
-      </c>
-      <c r="O10" s="8">
-        <v>-56.7</v>
+        <v>14.5</v>
+      </c>
+      <c r="O10" s="10">
+        <v>-91.4</v>
       </c>
       <c r="P10" s="9">
-        <v>6.2300000000000001E-2</v>
+        <v>2.3E-3</v>
       </c>
       <c r="Q10" s="10">
-        <v>1248.3</v>
+        <v>-91.4</v>
       </c>
     </row>
     <row r="11" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A11" s="6">
-        <v>44501</v>
+        <v>44531</v>
       </c>
       <c r="B11" s="7">
-        <v>65.099999999999994</v>
+        <v>78.099999999999994</v>
       </c>
       <c r="C11" s="7">
-        <v>78.099999999999994</v>
+        <v>82</v>
       </c>
       <c r="D11" s="7">
-        <v>86.3</v>
+        <v>88.3</v>
       </c>
       <c r="E11" s="7">
-        <v>62.1</v>
-      </c>
-      <c r="F11" s="10">
-        <v>13</v>
-      </c>
-      <c r="G11" s="10">
-        <v>19.97</v>
+        <v>77</v>
+      </c>
+      <c r="F11" s="8">
+        <v>3.9</v>
+      </c>
+      <c r="G11" s="8">
+        <v>4.99</v>
       </c>
       <c r="H11" s="9">
-        <v>2.8E-3</v>
-      </c>
-      <c r="I11" s="8">
-        <v>-10.9</v>
-      </c>
-      <c r="J11" s="9" t="s">
-        <v>17</v>
+        <v>2E-3</v>
+      </c>
+      <c r="I11" s="10">
+        <v>-29.8</v>
+      </c>
+      <c r="J11" s="10">
+        <v>-56.7</v>
       </c>
       <c r="K11" s="9">
-        <v>6.0299999999999999E-2</v>
-      </c>
-      <c r="L11" s="9" t="s">
-        <v>17</v>
+        <v>6.2300000000000001E-2</v>
+      </c>
+      <c r="L11" s="8">
+        <v>1248.3</v>
       </c>
       <c r="M11" s="9">
-        <v>2.8E-3</v>
-      </c>
-      <c r="N11" s="8">
-        <v>-10.9</v>
-      </c>
-      <c r="O11" s="9" t="s">
-        <v>17</v>
+        <v>2E-3</v>
+      </c>
+      <c r="N11" s="10">
+        <v>-29.8</v>
+      </c>
+      <c r="O11" s="10">
+        <v>-56.7</v>
       </c>
       <c r="P11" s="9">
-        <v>6.0299999999999999E-2</v>
-      </c>
-      <c r="Q11" s="9" t="s">
-        <v>17</v>
+        <v>6.2300000000000001E-2</v>
+      </c>
+      <c r="Q11" s="8">
+        <v>1248.3</v>
       </c>
     </row>
     <row r="12" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A12" s="6">
-        <v>44470</v>
+        <v>44501</v>
       </c>
       <c r="B12" s="7">
-        <v>68</v>
+        <v>65.099999999999994</v>
       </c>
       <c r="C12" s="7">
-        <v>65.099999999999994</v>
+        <v>78.099999999999994</v>
       </c>
       <c r="D12" s="7">
-        <v>68.2</v>
+        <v>86.3</v>
       </c>
       <c r="E12" s="7">
-        <v>62.8</v>
+        <v>62.1</v>
       </c>
       <c r="F12" s="8">
-        <v>-2.9</v>
+        <v>13</v>
       </c>
       <c r="G12" s="8">
-        <v>-4.26</v>
+        <v>19.97</v>
       </c>
       <c r="H12" s="9">
-        <v>3.2000000000000002E-3</v>
+        <v>2.8E-3</v>
       </c>
       <c r="I12" s="10">
-        <v>27.5</v>
+        <v>-10.9</v>
       </c>
       <c r="J12" s="9" t="s">
         <v>17</v>
       </c>
       <c r="K12" s="9">
-        <v>5.74E-2</v>
+        <v>6.0299999999999999E-2</v>
       </c>
       <c r="L12" s="9" t="s">
         <v>17</v>
       </c>
       <c r="M12" s="9">
-        <v>3.2000000000000002E-3</v>
+        <v>2.8E-3</v>
       </c>
       <c r="N12" s="10">
-        <v>27.5</v>
+        <v>-10.9</v>
       </c>
       <c r="O12" s="9" t="s">
         <v>17</v>
       </c>
       <c r="P12" s="9">
-        <v>5.74E-2</v>
+        <v>6.0299999999999999E-2</v>
       </c>
       <c r="Q12" s="9" t="s">
         <v>17</v>
@@ -1808,52 +1808,52 @@
     </row>
     <row r="13" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A13" s="6">
-        <v>44440</v>
+        <v>44470</v>
       </c>
       <c r="B13" s="7">
-        <v>74.400000000000006</v>
+        <v>68</v>
       </c>
       <c r="C13" s="7">
-        <v>68</v>
+        <v>65.099999999999994</v>
       </c>
       <c r="D13" s="7">
-        <v>75</v>
+        <v>68.2</v>
       </c>
       <c r="E13" s="7">
-        <v>66</v>
-      </c>
-      <c r="F13" s="8">
-        <v>-6.4</v>
-      </c>
-      <c r="G13" s="8">
-        <v>-8.6</v>
+        <v>62.8</v>
+      </c>
+      <c r="F13" s="10">
+        <v>-2.9</v>
+      </c>
+      <c r="G13" s="10">
+        <v>-4.26</v>
       </c>
       <c r="H13" s="9">
-        <v>2.5000000000000001E-3</v>
-      </c>
-      <c r="I13" s="10">
-        <v>169.9</v>
+        <v>3.2000000000000002E-3</v>
+      </c>
+      <c r="I13" s="8">
+        <v>27.5</v>
       </c>
       <c r="J13" s="9" t="s">
         <v>17</v>
       </c>
       <c r="K13" s="9">
-        <v>5.4199999999999998E-2</v>
+        <v>5.74E-2</v>
       </c>
       <c r="L13" s="9" t="s">
         <v>17</v>
       </c>
       <c r="M13" s="9">
-        <v>2.5000000000000001E-3</v>
-      </c>
-      <c r="N13" s="10">
-        <v>169.9</v>
+        <v>3.2000000000000002E-3</v>
+      </c>
+      <c r="N13" s="8">
+        <v>27.5</v>
       </c>
       <c r="O13" s="9" t="s">
         <v>17</v>
       </c>
       <c r="P13" s="9">
-        <v>5.4199999999999998E-2</v>
+        <v>5.74E-2</v>
       </c>
       <c r="Q13" s="9" t="s">
         <v>17</v>
@@ -1861,52 +1861,52 @@
     </row>
     <row r="14" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A14" s="6">
-        <v>44409</v>
+        <v>44440</v>
       </c>
       <c r="B14" s="7">
-        <v>78.900000000000006</v>
+        <v>74.400000000000006</v>
       </c>
       <c r="C14" s="7">
-        <v>74.400000000000006</v>
+        <v>68</v>
       </c>
       <c r="D14" s="7">
-        <v>80.099999999999994</v>
+        <v>75</v>
       </c>
       <c r="E14" s="7">
-        <v>73.7</v>
-      </c>
-      <c r="F14" s="8">
-        <v>-4.5</v>
-      </c>
-      <c r="G14" s="8">
-        <v>-5.7</v>
+        <v>66</v>
+      </c>
+      <c r="F14" s="10">
+        <v>-6.4</v>
+      </c>
+      <c r="G14" s="10">
+        <v>-8.6</v>
       </c>
       <c r="H14" s="9">
-        <v>8.9999999999999998E-4</v>
-      </c>
-      <c r="I14" s="10">
-        <v>181.8</v>
+        <v>2.5000000000000001E-3</v>
+      </c>
+      <c r="I14" s="8">
+        <v>169.9</v>
       </c>
       <c r="J14" s="9" t="s">
         <v>17</v>
       </c>
       <c r="K14" s="9">
-        <v>5.1700000000000003E-2</v>
+        <v>5.4199999999999998E-2</v>
       </c>
       <c r="L14" s="9" t="s">
         <v>17</v>
       </c>
       <c r="M14" s="9">
-        <v>8.9999999999999998E-4</v>
-      </c>
-      <c r="N14" s="10">
-        <v>181.8</v>
+        <v>2.5000000000000001E-3</v>
+      </c>
+      <c r="N14" s="8">
+        <v>169.9</v>
       </c>
       <c r="O14" s="9" t="s">
         <v>17</v>
       </c>
       <c r="P14" s="9">
-        <v>5.1700000000000003E-2</v>
+        <v>5.4199999999999998E-2</v>
       </c>
       <c r="Q14" s="9" t="s">
         <v>17</v>
@@ -1914,52 +1914,52 @@
     </row>
     <row r="15" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A15" s="6">
-        <v>44378</v>
+        <v>44409</v>
       </c>
       <c r="B15" s="7">
-        <v>82.7</v>
+        <v>78.900000000000006</v>
       </c>
       <c r="C15" s="7">
-        <v>78.900000000000006</v>
+        <v>74.400000000000006</v>
       </c>
       <c r="D15" s="7">
-        <v>83.3</v>
+        <v>80.099999999999994</v>
       </c>
       <c r="E15" s="7">
-        <v>75.8</v>
-      </c>
-      <c r="F15" s="8">
-        <v>-3.8</v>
-      </c>
-      <c r="G15" s="8">
-        <v>-4.59</v>
+        <v>73.7</v>
+      </c>
+      <c r="F15" s="10">
+        <v>-4.5</v>
+      </c>
+      <c r="G15" s="10">
+        <v>-5.7</v>
       </c>
       <c r="H15" s="9">
-        <v>2.9999999999999997E-4</v>
+        <v>8.9999999999999998E-4</v>
       </c>
       <c r="I15" s="8">
-        <v>-91.2</v>
+        <v>181.8</v>
       </c>
       <c r="J15" s="9" t="s">
         <v>17</v>
       </c>
       <c r="K15" s="9">
-        <v>5.0799999999999998E-2</v>
+        <v>5.1700000000000003E-2</v>
       </c>
       <c r="L15" s="9" t="s">
         <v>17</v>
       </c>
       <c r="M15" s="9">
-        <v>2.9999999999999997E-4</v>
+        <v>8.9999999999999998E-4</v>
       </c>
       <c r="N15" s="8">
-        <v>-91.2</v>
+        <v>181.8</v>
       </c>
       <c r="O15" s="9" t="s">
         <v>17</v>
       </c>
       <c r="P15" s="9">
-        <v>5.0799999999999998E-2</v>
+        <v>5.1700000000000003E-2</v>
       </c>
       <c r="Q15" s="9" t="s">
         <v>17</v>
@@ -1967,52 +1967,52 @@
     </row>
     <row r="16" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A16" s="6">
-        <v>44348</v>
+        <v>44378</v>
       </c>
       <c r="B16" s="7">
-        <v>83.5</v>
+        <v>82.7</v>
       </c>
       <c r="C16" s="7">
-        <v>82.7</v>
+        <v>78.900000000000006</v>
       </c>
       <c r="D16" s="7">
-        <v>99</v>
+        <v>83.3</v>
       </c>
       <c r="E16" s="7">
-        <v>81</v>
-      </c>
-      <c r="F16" s="8">
-        <v>-0.8</v>
-      </c>
-      <c r="G16" s="8">
-        <v>-0.96</v>
+        <v>75.8</v>
+      </c>
+      <c r="F16" s="10">
+        <v>-3.8</v>
+      </c>
+      <c r="G16" s="10">
+        <v>-4.59</v>
       </c>
       <c r="H16" s="9">
-        <v>3.7000000000000002E-3</v>
+        <v>2.9999999999999997E-4</v>
       </c>
       <c r="I16" s="10">
-        <v>314.39999999999998</v>
+        <v>-91.2</v>
       </c>
       <c r="J16" s="9" t="s">
         <v>17</v>
       </c>
       <c r="K16" s="9">
-        <v>5.0500000000000003E-2</v>
+        <v>5.0799999999999998E-2</v>
       </c>
       <c r="L16" s="9" t="s">
         <v>17</v>
       </c>
       <c r="M16" s="9">
-        <v>3.7000000000000002E-3</v>
+        <v>2.9999999999999997E-4</v>
       </c>
       <c r="N16" s="10">
-        <v>314.39999999999998</v>
+        <v>-91.2</v>
       </c>
       <c r="O16" s="9" t="s">
         <v>17</v>
       </c>
       <c r="P16" s="9">
-        <v>5.0500000000000003E-2</v>
+        <v>5.0799999999999998E-2</v>
       </c>
       <c r="Q16" s="9" t="s">
         <v>17</v>
@@ -2020,52 +2020,52 @@
     </row>
     <row r="17" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A17" s="6">
-        <v>44317</v>
+        <v>44348</v>
       </c>
       <c r="B17" s="7">
-        <v>84.8</v>
+        <v>83.5</v>
       </c>
       <c r="C17" s="7">
-        <v>83.5</v>
+        <v>82.7</v>
       </c>
       <c r="D17" s="7">
-        <v>93.4</v>
+        <v>99</v>
       </c>
       <c r="E17" s="7">
-        <v>71</v>
-      </c>
-      <c r="F17" s="8">
-        <v>-1.3</v>
-      </c>
-      <c r="G17" s="8">
-        <v>-1.53</v>
+        <v>81</v>
+      </c>
+      <c r="F17" s="10">
+        <v>-0.8</v>
+      </c>
+      <c r="G17" s="10">
+        <v>-0.96</v>
       </c>
       <c r="H17" s="9">
-        <v>8.9999999999999998E-4</v>
+        <v>3.7000000000000002E-3</v>
       </c>
       <c r="I17" s="8">
-        <v>-81.7</v>
+        <v>314.39999999999998</v>
       </c>
       <c r="J17" s="9" t="s">
         <v>17</v>
       </c>
       <c r="K17" s="9">
-        <v>4.6699999999999998E-2</v>
+        <v>5.0500000000000003E-2</v>
       </c>
       <c r="L17" s="9" t="s">
         <v>17</v>
       </c>
       <c r="M17" s="9">
-        <v>8.9999999999999998E-4</v>
+        <v>3.7000000000000002E-3</v>
       </c>
       <c r="N17" s="8">
-        <v>-81.7</v>
+        <v>314.39999999999998</v>
       </c>
       <c r="O17" s="9" t="s">
         <v>17</v>
       </c>
       <c r="P17" s="9">
-        <v>4.6699999999999998E-2</v>
+        <v>5.0500000000000003E-2</v>
       </c>
       <c r="Q17" s="9" t="s">
         <v>17</v>
@@ -2073,52 +2073,52 @@
     </row>
     <row r="18" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A18" s="6">
-        <v>44287</v>
+        <v>44317</v>
       </c>
       <c r="B18" s="7">
-        <v>88.6</v>
+        <v>84.8</v>
       </c>
       <c r="C18" s="7">
-        <v>84.8</v>
+        <v>83.5</v>
       </c>
       <c r="D18" s="7">
-        <v>91.4</v>
+        <v>93.4</v>
       </c>
       <c r="E18" s="7">
-        <v>83.4</v>
-      </c>
-      <c r="F18" s="8">
-        <v>-3.8</v>
-      </c>
-      <c r="G18" s="8">
-        <v>-4.29</v>
+        <v>71</v>
+      </c>
+      <c r="F18" s="10">
+        <v>-1.3</v>
+      </c>
+      <c r="G18" s="10">
+        <v>-1.53</v>
       </c>
       <c r="H18" s="9">
-        <v>4.8999999999999998E-3</v>
-      </c>
-      <c r="I18" s="8">
-        <v>-47.8</v>
+        <v>8.9999999999999998E-4</v>
+      </c>
+      <c r="I18" s="10">
+        <v>-81.7</v>
       </c>
       <c r="J18" s="9" t="s">
         <v>17</v>
       </c>
       <c r="K18" s="9">
-        <v>4.58E-2</v>
+        <v>4.6699999999999998E-2</v>
       </c>
       <c r="L18" s="9" t="s">
         <v>17</v>
       </c>
       <c r="M18" s="9">
-        <v>4.8999999999999998E-3</v>
-      </c>
-      <c r="N18" s="8">
-        <v>-47.8</v>
+        <v>8.9999999999999998E-4</v>
+      </c>
+      <c r="N18" s="10">
+        <v>-81.7</v>
       </c>
       <c r="O18" s="9" t="s">
         <v>17</v>
       </c>
       <c r="P18" s="9">
-        <v>4.58E-2</v>
+        <v>4.6699999999999998E-2</v>
       </c>
       <c r="Q18" s="9" t="s">
         <v>17</v>
@@ -2126,52 +2126,52 @@
     </row>
     <row r="19" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A19" s="6">
-        <v>44256</v>
+        <v>44287</v>
       </c>
       <c r="B19" s="7">
-        <v>88.8</v>
+        <v>88.6</v>
       </c>
       <c r="C19" s="7">
-        <v>88.6</v>
+        <v>84.8</v>
       </c>
       <c r="D19" s="7">
-        <v>97</v>
+        <v>91.4</v>
       </c>
       <c r="E19" s="7">
-        <v>87.1</v>
-      </c>
-      <c r="F19" s="8">
-        <v>-0.2</v>
-      </c>
-      <c r="G19" s="8">
-        <v>-0.23</v>
+        <v>83.4</v>
+      </c>
+      <c r="F19" s="10">
+        <v>-3.8</v>
+      </c>
+      <c r="G19" s="10">
+        <v>-4.29</v>
       </c>
       <c r="H19" s="9">
-        <v>9.4000000000000004E-3</v>
+        <v>4.8999999999999998E-3</v>
       </c>
       <c r="I19" s="10">
-        <v>89.6</v>
+        <v>-47.8</v>
       </c>
       <c r="J19" s="9" t="s">
         <v>17</v>
       </c>
       <c r="K19" s="9">
-        <v>4.0899999999999999E-2</v>
+        <v>4.58E-2</v>
       </c>
       <c r="L19" s="9" t="s">
         <v>17</v>
       </c>
       <c r="M19" s="9">
-        <v>9.4000000000000004E-3</v>
+        <v>4.8999999999999998E-3</v>
       </c>
       <c r="N19" s="10">
-        <v>89.6</v>
+        <v>-47.8</v>
       </c>
       <c r="O19" s="9" t="s">
         <v>17</v>
       </c>
       <c r="P19" s="9">
-        <v>4.0899999999999999E-2</v>
+        <v>4.58E-2</v>
       </c>
       <c r="Q19" s="9" t="s">
         <v>17</v>
@@ -2179,52 +2179,52 @@
     </row>
     <row r="20" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A20" s="6">
-        <v>44228</v>
+        <v>44256</v>
       </c>
       <c r="B20" s="7">
-        <v>90.3</v>
+        <v>88.8</v>
       </c>
       <c r="C20" s="7">
-        <v>88.8</v>
+        <v>88.6</v>
       </c>
       <c r="D20" s="7">
-        <v>100.5</v>
+        <v>97</v>
       </c>
       <c r="E20" s="7">
-        <v>86.3</v>
-      </c>
-      <c r="F20" s="8">
-        <v>-1.5</v>
-      </c>
-      <c r="G20" s="8">
-        <v>-1.66</v>
+        <v>87.1</v>
+      </c>
+      <c r="F20" s="10">
+        <v>-0.2</v>
+      </c>
+      <c r="G20" s="10">
+        <v>-0.23</v>
       </c>
       <c r="H20" s="9">
-        <v>5.0000000000000001E-3</v>
+        <v>9.4000000000000004E-3</v>
       </c>
       <c r="I20" s="8">
-        <v>-81.2</v>
+        <v>89.6</v>
       </c>
       <c r="J20" s="9" t="s">
         <v>17</v>
       </c>
       <c r="K20" s="9">
-        <v>3.15E-2</v>
+        <v>4.0899999999999999E-2</v>
       </c>
       <c r="L20" s="9" t="s">
         <v>17</v>
       </c>
       <c r="M20" s="9">
-        <v>5.0000000000000001E-3</v>
+        <v>9.4000000000000004E-3</v>
       </c>
       <c r="N20" s="8">
-        <v>-81.2</v>
+        <v>89.6</v>
       </c>
       <c r="O20" s="9" t="s">
         <v>17</v>
       </c>
       <c r="P20" s="9">
-        <v>3.15E-2</v>
+        <v>4.0899999999999999E-2</v>
       </c>
       <c r="Q20" s="9" t="s">
         <v>17</v>
@@ -2232,52 +2232,52 @@
     </row>
     <row r="21" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A21" s="6">
-        <v>44197</v>
+        <v>44228</v>
       </c>
       <c r="B21" s="7">
-        <v>91.5</v>
+        <v>90.3</v>
       </c>
       <c r="C21" s="7">
-        <v>90.3</v>
+        <v>88.8</v>
       </c>
       <c r="D21" s="7">
-        <v>115</v>
+        <v>100.5</v>
       </c>
       <c r="E21" s="7">
-        <v>71.8</v>
-      </c>
-      <c r="F21" s="8">
-        <v>-1.2</v>
-      </c>
-      <c r="G21" s="8">
-        <v>-1.31</v>
+        <v>86.3</v>
+      </c>
+      <c r="F21" s="10">
+        <v>-1.5</v>
+      </c>
+      <c r="G21" s="10">
+        <v>-1.66</v>
       </c>
       <c r="H21" s="9">
-        <v>2.6499999999999999E-2</v>
+        <v>5.0000000000000001E-3</v>
       </c>
       <c r="I21" s="10">
-        <v>473.4</v>
+        <v>-81.2</v>
       </c>
       <c r="J21" s="9" t="s">
         <v>17</v>
       </c>
       <c r="K21" s="9">
-        <v>2.6499999999999999E-2</v>
+        <v>3.15E-2</v>
       </c>
       <c r="L21" s="9" t="s">
         <v>17</v>
       </c>
       <c r="M21" s="9">
-        <v>2.6499999999999999E-2</v>
+        <v>5.0000000000000001E-3</v>
       </c>
       <c r="N21" s="10">
-        <v>473.4</v>
+        <v>-81.2</v>
       </c>
       <c r="O21" s="9" t="s">
         <v>17</v>
       </c>
       <c r="P21" s="9">
-        <v>2.6499999999999999E-2</v>
+        <v>3.15E-2</v>
       </c>
       <c r="Q21" s="9" t="s">
         <v>17</v>
@@ -2285,52 +2285,52 @@
     </row>
     <row r="22" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A22" s="6">
-        <v>44166</v>
+        <v>44197</v>
       </c>
       <c r="B22" s="7">
-        <v>67.400000000000006</v>
+        <v>91.5</v>
       </c>
       <c r="C22" s="7">
-        <v>91.5</v>
+        <v>90.3</v>
       </c>
       <c r="D22" s="7">
-        <v>105</v>
+        <v>115</v>
       </c>
       <c r="E22" s="7">
-        <v>49.55</v>
+        <v>71.8</v>
       </c>
       <c r="F22" s="10">
-        <v>24.1</v>
+        <v>-1.2</v>
       </c>
       <c r="G22" s="10">
-        <v>35.76</v>
+        <v>-1.31</v>
       </c>
       <c r="H22" s="9">
-        <v>4.5999999999999999E-3</v>
-      </c>
-      <c r="I22" s="9" t="s">
-        <v>17</v>
+        <v>2.6499999999999999E-2</v>
+      </c>
+      <c r="I22" s="8">
+        <v>473.4</v>
       </c>
       <c r="J22" s="9" t="s">
         <v>17</v>
       </c>
       <c r="K22" s="9">
-        <v>4.5999999999999999E-3</v>
+        <v>2.6499999999999999E-2</v>
       </c>
       <c r="L22" s="9" t="s">
         <v>17</v>
       </c>
       <c r="M22" s="9">
-        <v>4.5999999999999999E-3</v>
-      </c>
-      <c r="N22" s="9" t="s">
-        <v>17</v>
+        <v>2.6499999999999999E-2</v>
+      </c>
+      <c r="N22" s="8">
+        <v>473.4</v>
       </c>
       <c r="O22" s="9" t="s">
         <v>17</v>
       </c>
       <c r="P22" s="9">
-        <v>4.5999999999999999E-3</v>
+        <v>2.6499999999999999E-2</v>
       </c>
       <c r="Q22" s="9" t="s">
         <v>17</v>
@@ -2338,28 +2338,28 @@
     </row>
     <row r="23" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A23" s="6">
-        <v>44136</v>
+        <v>44166</v>
       </c>
       <c r="B23" s="7">
-        <v>73</v>
+        <v>67.400000000000006</v>
       </c>
       <c r="C23" s="7">
-        <v>67.400000000000006</v>
+        <v>91.5</v>
       </c>
       <c r="D23" s="7">
-        <v>78.599999999999994</v>
+        <v>105</v>
       </c>
       <c r="E23" s="7">
-        <v>67.400000000000006</v>
+        <v>49.55</v>
       </c>
       <c r="F23" s="8">
-        <v>-5.6</v>
+        <v>24.1</v>
       </c>
       <c r="G23" s="8">
-        <v>-7.67</v>
+        <v>35.76</v>
       </c>
       <c r="H23" s="9">
-        <v>0</v>
+        <v>4.5999999999999999E-3</v>
       </c>
       <c r="I23" s="9" t="s">
         <v>17</v>
@@ -2368,13 +2368,13 @@
         <v>17</v>
       </c>
       <c r="K23" s="9">
-        <v>0</v>
+        <v>4.5999999999999999E-3</v>
       </c>
       <c r="L23" s="9" t="s">
         <v>17</v>
       </c>
       <c r="M23" s="9">
-        <v>0</v>
+        <v>4.5999999999999999E-3</v>
       </c>
       <c r="N23" s="9" t="s">
         <v>17</v>
@@ -2383,7 +2383,7 @@
         <v>17</v>
       </c>
       <c r="P23" s="9">
-        <v>0</v>
+        <v>4.5999999999999999E-3</v>
       </c>
       <c r="Q23" s="9" t="s">
         <v>17</v>
@@ -2391,25 +2391,25 @@
     </row>
     <row r="24" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A24" s="6">
-        <v>44105</v>
+        <v>44136</v>
       </c>
       <c r="B24" s="7">
-        <v>76.8</v>
+        <v>73</v>
       </c>
       <c r="C24" s="7">
-        <v>73</v>
+        <v>67.400000000000006</v>
       </c>
       <c r="D24" s="7">
-        <v>80.900000000000006</v>
+        <v>78.599999999999994</v>
       </c>
       <c r="E24" s="7">
-        <v>72</v>
-      </c>
-      <c r="F24" s="8">
-        <v>-3.8</v>
-      </c>
-      <c r="G24" s="8">
-        <v>-4.95</v>
+        <v>67.400000000000006</v>
+      </c>
+      <c r="F24" s="10">
+        <v>-5.6</v>
+      </c>
+      <c r="G24" s="10">
+        <v>-7.67</v>
       </c>
       <c r="H24" s="9">
         <v>0</v>
@@ -2444,25 +2444,25 @@
     </row>
     <row r="25" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A25" s="6">
-        <v>44075</v>
+        <v>44105</v>
       </c>
       <c r="B25" s="7">
-        <v>78</v>
+        <v>76.8</v>
       </c>
       <c r="C25" s="7">
-        <v>76.8</v>
+        <v>73</v>
       </c>
       <c r="D25" s="7">
-        <v>87</v>
+        <v>80.900000000000006</v>
       </c>
       <c r="E25" s="7">
-        <v>70</v>
-      </c>
-      <c r="F25" s="8">
-        <v>-1.2</v>
-      </c>
-      <c r="G25" s="8">
-        <v>-1.54</v>
+        <v>72</v>
+      </c>
+      <c r="F25" s="10">
+        <v>-3.8</v>
+      </c>
+      <c r="G25" s="10">
+        <v>-4.95</v>
       </c>
       <c r="H25" s="9">
         <v>0</v>
@@ -2497,25 +2497,25 @@
     </row>
     <row r="26" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A26" s="6">
-        <v>44044</v>
+        <v>44075</v>
       </c>
       <c r="B26" s="7">
-        <v>87.9</v>
+        <v>78</v>
       </c>
       <c r="C26" s="7">
-        <v>78</v>
+        <v>76.8</v>
       </c>
       <c r="D26" s="7">
-        <v>88.3</v>
+        <v>87</v>
       </c>
       <c r="E26" s="7">
-        <v>69.5</v>
-      </c>
-      <c r="F26" s="8">
-        <v>-9.9</v>
-      </c>
-      <c r="G26" s="8">
-        <v>-11.26</v>
+        <v>70</v>
+      </c>
+      <c r="F26" s="10">
+        <v>-1.2</v>
+      </c>
+      <c r="G26" s="10">
+        <v>-1.54</v>
       </c>
       <c r="H26" s="9">
         <v>0</v>
@@ -2550,25 +2550,25 @@
     </row>
     <row r="27" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A27" s="6">
-        <v>44013</v>
+        <v>44044</v>
       </c>
       <c r="B27" s="7">
-        <v>69.900000000000006</v>
+        <v>87.9</v>
       </c>
       <c r="C27" s="7">
-        <v>87.9</v>
+        <v>78</v>
       </c>
       <c r="D27" s="7">
-        <v>176</v>
+        <v>88.3</v>
       </c>
       <c r="E27" s="7">
-        <v>67.099999999999994</v>
+        <v>69.5</v>
       </c>
       <c r="F27" s="10">
-        <v>18</v>
+        <v>-9.9</v>
       </c>
       <c r="G27" s="10">
-        <v>25.75</v>
+        <v>-11.26</v>
       </c>
       <c r="H27" s="9">
         <v>0</v>
@@ -2603,25 +2603,25 @@
     </row>
     <row r="28" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A28" s="6">
-        <v>43983</v>
+        <v>44013</v>
       </c>
       <c r="B28" s="7">
-        <v>32.299999999999997</v>
+        <v>69.900000000000006</v>
       </c>
       <c r="C28" s="7">
-        <v>69.900000000000006</v>
+        <v>87.9</v>
       </c>
       <c r="D28" s="7">
-        <v>88</v>
+        <v>176</v>
       </c>
       <c r="E28" s="7">
-        <v>32</v>
-      </c>
-      <c r="F28" s="10">
-        <v>37.6</v>
-      </c>
-      <c r="G28" s="10">
-        <v>116.41</v>
+        <v>67.099999999999994</v>
+      </c>
+      <c r="F28" s="8">
+        <v>18</v>
+      </c>
+      <c r="G28" s="8">
+        <v>25.75</v>
       </c>
       <c r="H28" s="9">
         <v>0</v>
@@ -2656,25 +2656,25 @@
     </row>
     <row r="29" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A29" s="6">
-        <v>43952</v>
+        <v>43983</v>
       </c>
       <c r="B29" s="7">
-        <v>24.7</v>
+        <v>32.299999999999997</v>
       </c>
       <c r="C29" s="7">
-        <v>32.299999999999997</v>
+        <v>69.900000000000006</v>
       </c>
       <c r="D29" s="7">
-        <v>39</v>
+        <v>88</v>
       </c>
       <c r="E29" s="7">
-        <v>24.15</v>
-      </c>
-      <c r="F29" s="10">
-        <v>7.6</v>
-      </c>
-      <c r="G29" s="10">
-        <v>30.77</v>
+        <v>32</v>
+      </c>
+      <c r="F29" s="8">
+        <v>37.6</v>
+      </c>
+      <c r="G29" s="8">
+        <v>116.41</v>
       </c>
       <c r="H29" s="9">
         <v>0</v>
@@ -2709,25 +2709,25 @@
     </row>
     <row r="30" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A30" s="6">
-        <v>43922</v>
+        <v>43952</v>
       </c>
       <c r="B30" s="7">
-        <v>18.3</v>
+        <v>24.7</v>
       </c>
       <c r="C30" s="7">
-        <v>24.7</v>
+        <v>32.299999999999997</v>
       </c>
       <c r="D30" s="7">
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="E30" s="7">
-        <v>18.5</v>
-      </c>
-      <c r="F30" s="10">
-        <v>6.4</v>
-      </c>
-      <c r="G30" s="10">
-        <v>34.97</v>
+        <v>24.15</v>
+      </c>
+      <c r="F30" s="8">
+        <v>7.6</v>
+      </c>
+      <c r="G30" s="8">
+        <v>30.77</v>
       </c>
       <c r="H30" s="9">
         <v>0</v>
@@ -2762,25 +2762,25 @@
     </row>
     <row r="31" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A31" s="6">
-        <v>43891</v>
+        <v>43922</v>
       </c>
       <c r="B31" s="7">
-        <v>24.31</v>
+        <v>18.3</v>
       </c>
       <c r="C31" s="7">
-        <v>18.3</v>
+        <v>24.7</v>
       </c>
       <c r="D31" s="7">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E31" s="7">
-        <v>17.3</v>
+        <v>18.5</v>
       </c>
       <c r="F31" s="8">
-        <v>-6.01</v>
+        <v>6.4</v>
       </c>
       <c r="G31" s="8">
-        <v>-24.72</v>
+        <v>34.97</v>
       </c>
       <c r="H31" s="9">
         <v>0</v>
@@ -2815,25 +2815,25 @@
     </row>
     <row r="32" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A32" s="6">
-        <v>43862</v>
+        <v>43891</v>
       </c>
       <c r="B32" s="7">
-        <v>24.8</v>
+        <v>24.31</v>
       </c>
       <c r="C32" s="7">
-        <v>24.31</v>
+        <v>18.3</v>
       </c>
       <c r="D32" s="7">
-        <v>25.01</v>
+        <v>25</v>
       </c>
       <c r="E32" s="7">
-        <v>23.22</v>
-      </c>
-      <c r="F32" s="8">
-        <v>-0.49</v>
-      </c>
-      <c r="G32" s="8">
-        <v>-1.98</v>
+        <v>17.3</v>
+      </c>
+      <c r="F32" s="10">
+        <v>-6.01</v>
+      </c>
+      <c r="G32" s="10">
+        <v>-24.72</v>
       </c>
       <c r="H32" s="9">
         <v>0</v>
@@ -2868,25 +2868,25 @@
     </row>
     <row r="33" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A33" s="6">
-        <v>43831</v>
+        <v>43862</v>
       </c>
       <c r="B33" s="7">
-        <v>25.2</v>
+        <v>24.8</v>
       </c>
       <c r="C33" s="7">
-        <v>24.8</v>
+        <v>24.31</v>
       </c>
       <c r="D33" s="7">
-        <v>26</v>
+        <v>25.01</v>
       </c>
       <c r="E33" s="7">
-        <v>23.5</v>
-      </c>
-      <c r="F33" s="8">
-        <v>-0.4</v>
-      </c>
-      <c r="G33" s="8">
-        <v>-1.59</v>
+        <v>23.22</v>
+      </c>
+      <c r="F33" s="10">
+        <v>-0.49</v>
+      </c>
+      <c r="G33" s="10">
+        <v>-1.98</v>
       </c>
       <c r="H33" s="9">
         <v>0</v>
@@ -2921,25 +2921,25 @@
     </row>
     <row r="34" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A34" s="6">
-        <v>43800</v>
+        <v>43831</v>
       </c>
       <c r="B34" s="7">
-        <v>23.7</v>
+        <v>25.2</v>
       </c>
       <c r="C34" s="7">
-        <v>25.2</v>
+        <v>24.8</v>
       </c>
       <c r="D34" s="7">
-        <v>26.6</v>
+        <v>26</v>
       </c>
       <c r="E34" s="7">
-        <v>22.74</v>
+        <v>23.5</v>
       </c>
       <c r="F34" s="10">
-        <v>1.5</v>
+        <v>-0.4</v>
       </c>
       <c r="G34" s="10">
-        <v>6.33</v>
+        <v>-1.59</v>
       </c>
       <c r="H34" s="9">
         <v>0</v>
@@ -2974,25 +2974,25 @@
     </row>
     <row r="35" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A35" s="6">
-        <v>43770</v>
+        <v>43800</v>
       </c>
       <c r="B35" s="7">
-        <v>23.2</v>
+        <v>23.7</v>
       </c>
       <c r="C35" s="7">
-        <v>23.7</v>
+        <v>25.2</v>
       </c>
       <c r="D35" s="7">
-        <v>27.2</v>
+        <v>26.6</v>
       </c>
       <c r="E35" s="7">
-        <v>22.5</v>
-      </c>
-      <c r="F35" s="10">
-        <v>0.5</v>
-      </c>
-      <c r="G35" s="10">
-        <v>2.16</v>
+        <v>22.74</v>
+      </c>
+      <c r="F35" s="8">
+        <v>1.5</v>
+      </c>
+      <c r="G35" s="8">
+        <v>6.33</v>
       </c>
       <c r="H35" s="9">
         <v>0</v>
@@ -3027,25 +3027,25 @@
     </row>
     <row r="36" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A36" s="6">
-        <v>43739</v>
+        <v>43770</v>
       </c>
       <c r="B36" s="7">
-        <v>20.9</v>
+        <v>23.2</v>
       </c>
       <c r="C36" s="7">
-        <v>23.2</v>
+        <v>23.7</v>
       </c>
       <c r="D36" s="7">
-        <v>26</v>
+        <v>27.2</v>
       </c>
       <c r="E36" s="7">
-        <v>19.399999999999999</v>
-      </c>
-      <c r="F36" s="10">
-        <v>2.2999999999999998</v>
-      </c>
-      <c r="G36" s="10">
-        <v>11</v>
+        <v>22.5</v>
+      </c>
+      <c r="F36" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="G36" s="8">
+        <v>2.16</v>
       </c>
       <c r="H36" s="9">
         <v>0</v>
@@ -3080,25 +3080,25 @@
     </row>
     <row r="37" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A37" s="6">
-        <v>43709</v>
+        <v>43739</v>
       </c>
       <c r="B37" s="7">
-        <v>24.51</v>
+        <v>20.9</v>
       </c>
       <c r="C37" s="7">
-        <v>20.9</v>
+        <v>23.2</v>
       </c>
       <c r="D37" s="7">
-        <v>24.96</v>
+        <v>26</v>
       </c>
       <c r="E37" s="7">
-        <v>20.83</v>
+        <v>19.399999999999999</v>
       </c>
       <c r="F37" s="8">
-        <v>-3.61</v>
+        <v>2.2999999999999998</v>
       </c>
       <c r="G37" s="8">
-        <v>-14.73</v>
+        <v>11</v>
       </c>
       <c r="H37" s="9">
         <v>0</v>
@@ -3133,25 +3133,25 @@
     </row>
     <row r="38" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A38" s="6">
-        <v>43678</v>
+        <v>43709</v>
       </c>
       <c r="B38" s="7">
-        <v>19.5</v>
+        <v>24.51</v>
       </c>
       <c r="C38" s="7">
-        <v>24.51</v>
+        <v>20.9</v>
       </c>
       <c r="D38" s="7">
-        <v>27.57</v>
+        <v>24.96</v>
       </c>
       <c r="E38" s="7">
-        <v>17.45</v>
+        <v>20.83</v>
       </c>
       <c r="F38" s="10">
-        <v>5.01</v>
+        <v>-3.61</v>
       </c>
       <c r="G38" s="10">
-        <v>25.69</v>
+        <v>-14.73</v>
       </c>
       <c r="H38" s="9">
         <v>0</v>
@@ -3186,25 +3186,25 @@
     </row>
     <row r="39" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A39" s="6">
-        <v>43647</v>
+        <v>43678</v>
       </c>
       <c r="B39" s="7">
-        <v>24.62</v>
+        <v>19.5</v>
       </c>
       <c r="C39" s="7">
-        <v>19.5</v>
+        <v>24.51</v>
       </c>
       <c r="D39" s="7">
-        <v>24.1</v>
+        <v>27.57</v>
       </c>
       <c r="E39" s="7">
-        <v>19</v>
+        <v>17.45</v>
       </c>
       <c r="F39" s="8">
-        <v>-5.12</v>
+        <v>5.01</v>
       </c>
       <c r="G39" s="8">
-        <v>-20.8</v>
+        <v>25.69</v>
       </c>
       <c r="H39" s="9">
         <v>0</v>
@@ -3239,25 +3239,25 @@
     </row>
     <row r="40" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A40" s="6">
-        <v>43617</v>
+        <v>43647</v>
       </c>
       <c r="B40" s="7">
-        <v>28.2</v>
+        <v>24.62</v>
       </c>
       <c r="C40" s="7">
-        <v>24.62</v>
+        <v>19.5</v>
       </c>
       <c r="D40" s="7">
-        <v>28.2</v>
+        <v>24.1</v>
       </c>
       <c r="E40" s="7">
-        <v>21.1</v>
-      </c>
-      <c r="F40" s="8">
-        <v>-3.58</v>
-      </c>
-      <c r="G40" s="8">
-        <v>-12.7</v>
+        <v>19</v>
+      </c>
+      <c r="F40" s="10">
+        <v>-5.12</v>
+      </c>
+      <c r="G40" s="10">
+        <v>-20.8</v>
       </c>
       <c r="H40" s="9">
         <v>0</v>
@@ -3292,25 +3292,25 @@
     </row>
     <row r="41" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A41" s="6">
-        <v>43586</v>
+        <v>43617</v>
       </c>
       <c r="B41" s="7">
-        <v>29.8</v>
+        <v>28.2</v>
       </c>
       <c r="C41" s="7">
+        <v>24.62</v>
+      </c>
+      <c r="D41" s="7">
         <v>28.2</v>
       </c>
-      <c r="D41" s="7">
-        <v>31.3</v>
-      </c>
       <c r="E41" s="7">
-        <v>27.55</v>
-      </c>
-      <c r="F41" s="8">
-        <v>-1.6</v>
-      </c>
-      <c r="G41" s="8">
-        <v>-5.37</v>
+        <v>21.1</v>
+      </c>
+      <c r="F41" s="10">
+        <v>-3.58</v>
+      </c>
+      <c r="G41" s="10">
+        <v>-12.7</v>
       </c>
       <c r="H41" s="9">
         <v>0</v>
@@ -3345,25 +3345,25 @@
     </row>
     <row r="42" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A42" s="6">
-        <v>43556</v>
+        <v>43586</v>
       </c>
       <c r="B42" s="7">
-        <v>26.73</v>
+        <v>29.8</v>
       </c>
       <c r="C42" s="7">
-        <v>29.8</v>
+        <v>28.2</v>
       </c>
       <c r="D42" s="7">
-        <v>36</v>
+        <v>31.3</v>
       </c>
       <c r="E42" s="7">
-        <v>27</v>
+        <v>27.55</v>
       </c>
       <c r="F42" s="10">
-        <v>3.07</v>
+        <v>-1.6</v>
       </c>
       <c r="G42" s="10">
-        <v>11.49</v>
+        <v>-5.37</v>
       </c>
       <c r="H42" s="9">
         <v>0</v>
@@ -3398,25 +3398,25 @@
     </row>
     <row r="43" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A43" s="6">
-        <v>43525</v>
+        <v>43556</v>
       </c>
       <c r="B43" s="7">
-        <v>17.510000000000002</v>
+        <v>26.73</v>
       </c>
       <c r="C43" s="7">
-        <v>26.73</v>
+        <v>29.8</v>
       </c>
       <c r="D43" s="7">
-        <v>27.81</v>
+        <v>36</v>
       </c>
       <c r="E43" s="7">
-        <v>17.559999999999999</v>
-      </c>
-      <c r="F43" s="10">
-        <v>9.2200000000000006</v>
-      </c>
-      <c r="G43" s="10">
-        <v>52.66</v>
+        <v>27</v>
+      </c>
+      <c r="F43" s="8">
+        <v>3.07</v>
+      </c>
+      <c r="G43" s="8">
+        <v>11.49</v>
       </c>
       <c r="H43" s="9">
         <v>0</v>
@@ -3451,25 +3451,25 @@
     </row>
     <row r="44" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A44" s="6">
-        <v>43497</v>
+        <v>43525</v>
       </c>
       <c r="B44" s="7">
-        <v>17</v>
+        <v>17.510000000000002</v>
       </c>
       <c r="C44" s="7">
-        <v>17.510000000000002</v>
+        <v>26.73</v>
       </c>
       <c r="D44" s="7">
-        <v>18.149999999999999</v>
+        <v>27.81</v>
       </c>
       <c r="E44" s="7">
-        <v>16.16</v>
-      </c>
-      <c r="F44" s="10">
-        <v>0.51</v>
-      </c>
-      <c r="G44" s="10">
-        <v>3</v>
+        <v>17.559999999999999</v>
+      </c>
+      <c r="F44" s="8">
+        <v>9.2200000000000006</v>
+      </c>
+      <c r="G44" s="8">
+        <v>52.66</v>
       </c>
       <c r="H44" s="9">
         <v>0</v>
@@ -3504,25 +3504,25 @@
     </row>
     <row r="45" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A45" s="6">
-        <v>43466</v>
+        <v>43497</v>
       </c>
       <c r="B45" s="7">
-        <v>13.89</v>
+        <v>17</v>
       </c>
       <c r="C45" s="7">
-        <v>17</v>
+        <v>17.510000000000002</v>
       </c>
       <c r="D45" s="7">
-        <v>18.940000000000001</v>
+        <v>18.149999999999999</v>
       </c>
       <c r="E45" s="7">
-        <v>13.37</v>
-      </c>
-      <c r="F45" s="10">
-        <v>3.11</v>
-      </c>
-      <c r="G45" s="10">
-        <v>22.39</v>
+        <v>16.16</v>
+      </c>
+      <c r="F45" s="8">
+        <v>0.51</v>
+      </c>
+      <c r="G45" s="8">
+        <v>3</v>
       </c>
       <c r="H45" s="9">
         <v>0</v>
@@ -3557,25 +3557,25 @@
     </row>
     <row r="46" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A46" s="6">
-        <v>43435</v>
+        <v>43466</v>
       </c>
       <c r="B46" s="7">
-        <v>14.05</v>
+        <v>13.89</v>
       </c>
       <c r="C46" s="7">
-        <v>13.89</v>
+        <v>17</v>
       </c>
       <c r="D46" s="7">
-        <v>14.31</v>
+        <v>18.940000000000001</v>
       </c>
       <c r="E46" s="7">
-        <v>12.95</v>
+        <v>13.37</v>
       </c>
       <c r="F46" s="8">
-        <v>-0.16</v>
+        <v>3.11</v>
       </c>
       <c r="G46" s="8">
-        <v>-1.1399999999999999</v>
+        <v>22.39</v>
       </c>
       <c r="H46" s="9">
         <v>0</v>
@@ -3610,25 +3610,25 @@
     </row>
     <row r="47" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A47" s="6">
-        <v>43405</v>
+        <v>43435</v>
       </c>
       <c r="B47" s="7">
-        <v>16.399999999999999</v>
+        <v>14.05</v>
       </c>
       <c r="C47" s="7">
-        <v>14.05</v>
+        <v>13.89</v>
       </c>
       <c r="D47" s="7">
-        <v>16</v>
+        <v>14.31</v>
       </c>
       <c r="E47" s="7">
-        <v>13.4</v>
-      </c>
-      <c r="F47" s="8">
-        <v>-2.35</v>
-      </c>
-      <c r="G47" s="8">
-        <v>-14.33</v>
+        <v>12.95</v>
+      </c>
+      <c r="F47" s="10">
+        <v>-0.16</v>
+      </c>
+      <c r="G47" s="10">
+        <v>-1.1399999999999999</v>
       </c>
       <c r="H47" s="9">
         <v>0</v>
@@ -3663,25 +3663,25 @@
     </row>
     <row r="48" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A48" s="6">
-        <v>43374</v>
+        <v>43405</v>
       </c>
       <c r="B48" s="7">
-        <v>22</v>
+        <v>16.399999999999999</v>
       </c>
       <c r="C48" s="7">
-        <v>16.399999999999999</v>
+        <v>14.05</v>
       </c>
       <c r="D48" s="7">
-        <v>22.31</v>
+        <v>16</v>
       </c>
       <c r="E48" s="7">
-        <v>15.69</v>
-      </c>
-      <c r="F48" s="8">
-        <v>-5.6</v>
-      </c>
-      <c r="G48" s="8">
-        <v>-25.45</v>
+        <v>13.4</v>
+      </c>
+      <c r="F48" s="10">
+        <v>-2.35</v>
+      </c>
+      <c r="G48" s="10">
+        <v>-14.33</v>
       </c>
       <c r="H48" s="9">
         <v>0</v>
@@ -3716,25 +3716,25 @@
     </row>
     <row r="49" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A49" s="6">
-        <v>43344</v>
+        <v>43374</v>
       </c>
       <c r="B49" s="7">
-        <v>19.899999999999999</v>
+        <v>22</v>
       </c>
       <c r="C49" s="7">
-        <v>22</v>
+        <v>16.399999999999999</v>
       </c>
       <c r="D49" s="7">
-        <v>22</v>
+        <v>22.31</v>
       </c>
       <c r="E49" s="7">
-        <v>19.55</v>
+        <v>15.69</v>
       </c>
       <c r="F49" s="10">
-        <v>2.1</v>
+        <v>-5.6</v>
       </c>
       <c r="G49" s="10">
-        <v>10.55</v>
+        <v>-25.45</v>
       </c>
       <c r="H49" s="9">
         <v>0</v>
@@ -3769,25 +3769,25 @@
     </row>
     <row r="50" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A50" s="6">
-        <v>43313</v>
+        <v>43344</v>
       </c>
       <c r="B50" s="7">
-        <v>23.76</v>
+        <v>19.899999999999999</v>
       </c>
       <c r="C50" s="7">
-        <v>19.899999999999999</v>
+        <v>22</v>
       </c>
       <c r="D50" s="7">
-        <v>23.76</v>
+        <v>22</v>
       </c>
       <c r="E50" s="7">
-        <v>16.25</v>
+        <v>19.55</v>
       </c>
       <c r="F50" s="8">
-        <v>-3.86</v>
+        <v>2.1</v>
       </c>
       <c r="G50" s="8">
-        <v>-16.25</v>
+        <v>10.55</v>
       </c>
       <c r="H50" s="9">
         <v>0</v>
@@ -3822,25 +3822,25 @@
     </row>
     <row r="51" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A51" s="6">
-        <v>43282</v>
+        <v>43313</v>
       </c>
       <c r="B51" s="7">
-        <v>25</v>
+        <v>23.76</v>
       </c>
       <c r="C51" s="7">
+        <v>19.899999999999999</v>
+      </c>
+      <c r="D51" s="7">
         <v>23.76</v>
       </c>
-      <c r="D51" s="7">
-        <v>25.5</v>
-      </c>
       <c r="E51" s="7">
-        <v>23.56</v>
-      </c>
-      <c r="F51" s="8">
-        <v>-1.24</v>
-      </c>
-      <c r="G51" s="8">
-        <v>-4.96</v>
+        <v>16.25</v>
+      </c>
+      <c r="F51" s="10">
+        <v>-3.86</v>
+      </c>
+      <c r="G51" s="10">
+        <v>-16.25</v>
       </c>
       <c r="H51" s="9">
         <v>0</v>
@@ -3875,25 +3875,25 @@
     </row>
     <row r="52" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A52" s="6">
-        <v>43252</v>
+        <v>43282</v>
       </c>
       <c r="B52" s="7">
-        <v>26.5</v>
+        <v>25</v>
       </c>
       <c r="C52" s="7">
-        <v>25</v>
+        <v>23.76</v>
       </c>
       <c r="D52" s="7">
-        <v>26.99</v>
+        <v>25.5</v>
       </c>
       <c r="E52" s="7">
-        <v>25</v>
-      </c>
-      <c r="F52" s="8">
-        <v>-1.5</v>
-      </c>
-      <c r="G52" s="8">
-        <v>-5.66</v>
+        <v>23.56</v>
+      </c>
+      <c r="F52" s="10">
+        <v>-1.24</v>
+      </c>
+      <c r="G52" s="10">
+        <v>-4.96</v>
       </c>
       <c r="H52" s="9">
         <v>0</v>
@@ -3928,25 +3928,25 @@
     </row>
     <row r="53" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A53" s="6">
-        <v>43221</v>
+        <v>43252</v>
       </c>
       <c r="B53" s="7">
-        <v>27.36</v>
+        <v>26.5</v>
       </c>
       <c r="C53" s="7">
-        <v>26.5</v>
+        <v>25</v>
       </c>
       <c r="D53" s="7">
-        <v>27.36</v>
+        <v>26.99</v>
       </c>
       <c r="E53" s="7">
-        <v>26</v>
-      </c>
-      <c r="F53" s="8">
-        <v>-0.86</v>
-      </c>
-      <c r="G53" s="8">
-        <v>-3.14</v>
+        <v>25</v>
+      </c>
+      <c r="F53" s="10">
+        <v>-1.5</v>
+      </c>
+      <c r="G53" s="10">
+        <v>-5.66</v>
       </c>
       <c r="H53" s="9">
         <v>0</v>
@@ -3981,25 +3981,25 @@
     </row>
     <row r="54" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A54" s="6">
-        <v>43191</v>
+        <v>43221</v>
       </c>
       <c r="B54" s="7">
-        <v>28</v>
+        <v>27.36</v>
       </c>
       <c r="C54" s="7">
+        <v>26.5</v>
+      </c>
+      <c r="D54" s="7">
         <v>27.36</v>
       </c>
-      <c r="D54" s="7">
-        <v>28.21</v>
-      </c>
       <c r="E54" s="7">
-        <v>26.2</v>
-      </c>
-      <c r="F54" s="8">
-        <v>-0.64</v>
-      </c>
-      <c r="G54" s="8">
-        <v>-2.29</v>
+        <v>26</v>
+      </c>
+      <c r="F54" s="10">
+        <v>-0.86</v>
+      </c>
+      <c r="G54" s="10">
+        <v>-3.14</v>
       </c>
       <c r="H54" s="9">
         <v>0</v>
@@ -4034,25 +4034,25 @@
     </row>
     <row r="55" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A55" s="6">
-        <v>43160</v>
+        <v>43191</v>
       </c>
       <c r="B55" s="7">
-        <v>26.8</v>
+        <v>28</v>
       </c>
       <c r="C55" s="7">
-        <v>28</v>
+        <v>27.36</v>
       </c>
       <c r="D55" s="7">
-        <v>28.09</v>
+        <v>28.21</v>
       </c>
       <c r="E55" s="7">
-        <v>26.6</v>
+        <v>26.2</v>
       </c>
       <c r="F55" s="10">
-        <v>1.2</v>
+        <v>-0.64</v>
       </c>
       <c r="G55" s="10">
-        <v>4.4800000000000004</v>
+        <v>-2.29</v>
       </c>
       <c r="H55" s="9">
         <v>0</v>
@@ -4087,25 +4087,25 @@
     </row>
     <row r="56" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A56" s="6">
-        <v>43132</v>
+        <v>43160</v>
       </c>
       <c r="B56" s="7">
-        <v>27</v>
+        <v>26.8</v>
       </c>
       <c r="C56" s="7">
-        <v>26.8</v>
+        <v>28</v>
       </c>
       <c r="D56" s="7">
-        <v>28</v>
+        <v>28.09</v>
       </c>
       <c r="E56" s="7">
-        <v>25.46</v>
+        <v>26.6</v>
       </c>
       <c r="F56" s="8">
-        <v>-0.2</v>
+        <v>1.2</v>
       </c>
       <c r="G56" s="8">
-        <v>-0.74</v>
+        <v>4.4800000000000004</v>
       </c>
       <c r="H56" s="9">
         <v>0</v>
@@ -4140,25 +4140,25 @@
     </row>
     <row r="57" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A57" s="6">
-        <v>43101</v>
+        <v>43132</v>
       </c>
       <c r="B57" s="7">
-        <v>25.07</v>
+        <v>27</v>
       </c>
       <c r="C57" s="7">
-        <v>27</v>
+        <v>26.8</v>
       </c>
       <c r="D57" s="7">
-        <v>27.2</v>
+        <v>28</v>
       </c>
       <c r="E57" s="7">
-        <v>23.01</v>
+        <v>25.46</v>
       </c>
       <c r="F57" s="10">
-        <v>1.93</v>
+        <v>-0.2</v>
       </c>
       <c r="G57" s="10">
-        <v>7.7</v>
+        <v>-0.74</v>
       </c>
       <c r="H57" s="9">
         <v>0</v>
@@ -4193,25 +4193,25 @@
     </row>
     <row r="58" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A58" s="6">
-        <v>43070</v>
+        <v>43101</v>
       </c>
       <c r="B58" s="7">
-        <v>25.32</v>
+        <v>25.07</v>
       </c>
       <c r="C58" s="7">
-        <v>25.07</v>
+        <v>27</v>
       </c>
       <c r="D58" s="7">
-        <v>26.29</v>
+        <v>27.2</v>
       </c>
       <c r="E58" s="7">
-        <v>23.46</v>
+        <v>23.01</v>
       </c>
       <c r="F58" s="8">
-        <v>-0.25</v>
+        <v>1.93</v>
       </c>
       <c r="G58" s="8">
-        <v>-0.99</v>
+        <v>7.7</v>
       </c>
       <c r="H58" s="9">
         <v>0</v>
@@ -4246,25 +4246,25 @@
     </row>
     <row r="59" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A59" s="6">
-        <v>43040</v>
+        <v>43070</v>
       </c>
       <c r="B59" s="7">
-        <v>25</v>
+        <v>25.32</v>
       </c>
       <c r="C59" s="7">
-        <v>25.32</v>
+        <v>25.07</v>
       </c>
       <c r="D59" s="7">
-        <v>28</v>
+        <v>26.29</v>
       </c>
       <c r="E59" s="7">
-        <v>25</v>
+        <v>23.46</v>
       </c>
       <c r="F59" s="10">
-        <v>0.32</v>
+        <v>-0.25</v>
       </c>
       <c r="G59" s="10">
-        <v>1.28</v>
+        <v>-0.99</v>
       </c>
       <c r="H59" s="9">
         <v>0</v>
@@ -4299,25 +4299,25 @@
     </row>
     <row r="60" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A60" s="6">
-        <v>43009</v>
+        <v>43040</v>
       </c>
       <c r="B60" s="7">
-        <v>31.1</v>
+        <v>25</v>
       </c>
       <c r="C60" s="7">
-        <v>25</v>
+        <v>25.32</v>
       </c>
       <c r="D60" s="7">
-        <v>31.57</v>
+        <v>28</v>
       </c>
       <c r="E60" s="7">
         <v>25</v>
       </c>
       <c r="F60" s="8">
-        <v>-6.1</v>
+        <v>0.32</v>
       </c>
       <c r="G60" s="8">
-        <v>-19.61</v>
+        <v>1.28</v>
       </c>
       <c r="H60" s="9">
         <v>0</v>
@@ -4352,25 +4352,25 @@
     </row>
     <row r="61" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A61" s="6">
-        <v>42979</v>
+        <v>43009</v>
       </c>
       <c r="B61" s="7">
-        <v>30.6</v>
+        <v>31.1</v>
       </c>
       <c r="C61" s="7">
-        <v>31.1</v>
+        <v>25</v>
       </c>
       <c r="D61" s="7">
-        <v>32</v>
+        <v>31.57</v>
       </c>
       <c r="E61" s="7">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="F61" s="10">
-        <v>0.5</v>
+        <v>-6.1</v>
       </c>
       <c r="G61" s="10">
-        <v>1.63</v>
+        <v>-19.61</v>
       </c>
       <c r="H61" s="9">
         <v>0</v>
@@ -4405,25 +4405,25 @@
     </row>
     <row r="62" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A62" s="6">
-        <v>42948</v>
+        <v>42979</v>
       </c>
       <c r="B62" s="7">
-        <v>35.49</v>
+        <v>30.6</v>
       </c>
       <c r="C62" s="7">
-        <v>30.6</v>
+        <v>31.1</v>
       </c>
       <c r="D62" s="7">
-        <v>35.49</v>
+        <v>32</v>
       </c>
       <c r="E62" s="7">
-        <v>30.4</v>
+        <v>30</v>
       </c>
       <c r="F62" s="8">
-        <v>-4.8899999999999997</v>
+        <v>0.5</v>
       </c>
       <c r="G62" s="8">
-        <v>-13.78</v>
+        <v>1.63</v>
       </c>
       <c r="H62" s="9">
         <v>0</v>
@@ -4458,25 +4458,25 @@
     </row>
     <row r="63" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A63" s="6">
-        <v>42917</v>
+        <v>42948</v>
       </c>
       <c r="B63" s="7">
-        <v>50</v>
+        <v>35.49</v>
       </c>
       <c r="C63" s="7">
+        <v>30.6</v>
+      </c>
+      <c r="D63" s="7">
         <v>35.49</v>
       </c>
-      <c r="D63" s="7">
-        <v>46.9</v>
-      </c>
       <c r="E63" s="7">
-        <v>34.200000000000003</v>
-      </c>
-      <c r="F63" s="8">
-        <v>-14.51</v>
-      </c>
-      <c r="G63" s="8">
-        <v>-29.02</v>
+        <v>30.4</v>
+      </c>
+      <c r="F63" s="10">
+        <v>-4.8899999999999997</v>
+      </c>
+      <c r="G63" s="10">
+        <v>-13.78</v>
       </c>
       <c r="H63" s="9">
         <v>0</v>
@@ -4511,25 +4511,25 @@
     </row>
     <row r="64" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A64" s="6">
-        <v>42887</v>
+        <v>42917</v>
       </c>
       <c r="B64" s="7">
-        <v>49.8</v>
+        <v>50</v>
       </c>
       <c r="C64" s="7">
-        <v>50</v>
+        <v>35.49</v>
       </c>
       <c r="D64" s="7">
-        <v>53.5</v>
+        <v>46.9</v>
       </c>
       <c r="E64" s="7">
-        <v>42</v>
-      </c>
-      <c r="F64" s="8">
-        <v>-0.8</v>
-      </c>
-      <c r="G64" s="8">
-        <v>-1.57</v>
+        <v>34.200000000000003</v>
+      </c>
+      <c r="F64" s="10">
+        <v>-14.51</v>
+      </c>
+      <c r="G64" s="10">
+        <v>-29.02</v>
       </c>
       <c r="H64" s="9">
         <v>0</v>
@@ -4564,25 +4564,25 @@
     </row>
     <row r="65" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A65" s="6">
-        <v>42856</v>
-      </c>
-      <c r="B65" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="C65" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="D65" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="E65" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="F65" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="G65" s="9" t="s">
-        <v>17</v>
+        <v>42887</v>
+      </c>
+      <c r="B65" s="7">
+        <v>49.8</v>
+      </c>
+      <c r="C65" s="7">
+        <v>50</v>
+      </c>
+      <c r="D65" s="7">
+        <v>53.5</v>
+      </c>
+      <c r="E65" s="7">
+        <v>42</v>
+      </c>
+      <c r="F65" s="10">
+        <v>-0.8</v>
+      </c>
+      <c r="G65" s="10">
+        <v>-1.57</v>
       </c>
       <c r="H65" s="9">
         <v>0</v>
@@ -4617,54 +4617,107 @@
     </row>
     <row r="66" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A66" s="6">
+        <v>42856</v>
+      </c>
+      <c r="B66" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C66" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D66" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E66" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F66" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G66" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H66" s="9">
+        <v>0</v>
+      </c>
+      <c r="I66" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J66" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="K66" s="9">
+        <v>0</v>
+      </c>
+      <c r="L66" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="M66" s="9">
+        <v>0</v>
+      </c>
+      <c r="N66" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="O66" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="P66" s="9">
+        <v>0</v>
+      </c>
+      <c r="Q66" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="67" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A67" s="6">
         <v>42826</v>
       </c>
-      <c r="B66" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="C66" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="D66" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="E66" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="F66" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="G66" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="H66" s="9">
-        <v>0</v>
-      </c>
-      <c r="I66" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="J66" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="K66" s="9">
-        <v>0</v>
-      </c>
-      <c r="L66" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="M66" s="9">
-        <v>0</v>
-      </c>
-      <c r="N66" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="O66" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="P66" s="9">
-        <v>0</v>
-      </c>
-      <c r="Q66" s="9" t="s">
+      <c r="B67" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C67" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D67" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E67" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F67" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G67" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H67" s="9">
+        <v>0</v>
+      </c>
+      <c r="I67" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J67" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="K67" s="9">
+        <v>0</v>
+      </c>
+      <c r="L67" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="M67" s="9">
+        <v>0</v>
+      </c>
+      <c r="N67" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="O67" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="P67" s="9">
+        <v>0</v>
+      </c>
+      <c r="Q67" s="9" t="s">
         <v>17</v>
       </c>
     </row>
